--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_individual_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_individual_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.008508942972900661</v>
       </c>
       <c r="C2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>44107178</v>
+        <v>3992034</v>
       </c>
       <c r="L2" t="n">
-        <v>23336422</v>
+        <v>1743863</v>
       </c>
       <c r="M2" t="n">
-        <v>5340802</v>
+        <v>363498</v>
       </c>
       <c r="N2" t="n">
-        <v>187004</v>
+        <v>8455</v>
       </c>
       <c r="O2" t="n">
-        <v>3182671</v>
+        <v>205912</v>
       </c>
       <c r="P2" t="n">
-        <v>1242855</v>
+        <v>77937</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998540282249451</v>
+        <v>0.9998567700386047</v>
       </c>
       <c r="R2" t="n">
-        <v>0.842592179775238</v>
+        <v>0.740113377571106</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7148997783660889</v>
+        <v>0.553671658039093</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6344461441040039</v>
+        <v>0.4302683174610138</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1758837550878525</v>
+        <v>0.06537185609340668</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6855859756469727</v>
+        <v>0.484889030456543</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7898876070976257</v>
+        <v>0.6163415312767029</v>
       </c>
       <c r="X2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>48303112</v>
+        <v>4789433</v>
       </c>
       <c r="AG2" t="n">
-        <v>29981680</v>
+        <v>3027015</v>
       </c>
       <c r="AH2" t="n">
-        <v>8027267</v>
+        <v>807060</v>
       </c>
       <c r="AI2" t="n">
-        <v>591860</v>
+        <v>59367</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4598515</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560742974281311</v>
+        <v>0.9549785256385803</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911531388759613</v>
+        <v>0.912082850933075</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580335974693298</v>
+        <v>0.8579939603805542</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.661676824092865</v>
+        <v>0.6605360507965088</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019646048545837</v>
+        <v>0.90191650390625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002036865544291333</v>
       </c>
       <c r="C3" t="n">
-        <v>6979</v>
+        <v>707</v>
       </c>
       <c r="D3" t="n">
-        <v>44107178</v>
+        <v>3992034</v>
       </c>
       <c r="E3" t="n">
-        <v>6101655</v>
+        <v>950594</v>
       </c>
       <c r="F3" t="n">
-        <v>197453</v>
+        <v>51043</v>
       </c>
       <c r="G3" t="n">
-        <v>17608</v>
+        <v>4325</v>
       </c>
       <c r="H3" t="n">
-        <v>14030</v>
+        <v>3963</v>
       </c>
       <c r="I3" t="n">
-        <v>960</v>
+        <v>324</v>
       </c>
       <c r="J3" t="n">
-        <v>100686936</v>
+        <v>10068711</v>
       </c>
       <c r="K3" t="n">
-        <v>105474308</v>
+        <v>10011230</v>
       </c>
       <c r="L3" t="n">
-        <v>121900174</v>
+        <v>11681844</v>
       </c>
       <c r="M3" t="n">
-        <v>151717273</v>
+        <v>14992157</v>
       </c>
       <c r="N3" t="n">
-        <v>162388431</v>
+        <v>16205140</v>
       </c>
       <c r="O3" t="n">
-        <v>157598826</v>
+        <v>15685316</v>
       </c>
       <c r="P3" t="n">
-        <v>161894784</v>
+        <v>16173681</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8743467926979065</v>
+        <v>0.7979296445846558</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7081660628318787</v>
+        <v>0.5239366888999939</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5702649354934692</v>
+        <v>0.3856644630432129</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2088618129491806</v>
+        <v>0.09396741539239883</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6238597631454468</v>
+        <v>0.4022205770015717</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6424307823181152</v>
+        <v>0.4021413326263428</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>48303112</v>
+        <v>4789433</v>
       </c>
       <c r="Z3" t="n">
-        <v>1988133</v>
+        <v>198166</v>
       </c>
       <c r="AA3" t="n">
-        <v>85525</v>
+        <v>8476</v>
       </c>
       <c r="AB3" t="n">
-        <v>68445</v>
+        <v>6874</v>
       </c>
       <c r="AC3" t="n">
-        <v>348</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100696200</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>111494909</v>
+        <v>11187217</v>
       </c>
       <c r="AG3" t="n">
-        <v>128296811</v>
+        <v>12795836</v>
       </c>
       <c r="AH3" t="n">
-        <v>153466369</v>
+        <v>15339900</v>
       </c>
       <c r="AI3" t="n">
-        <v>162962027</v>
+        <v>16295512</v>
       </c>
       <c r="AJ3" t="n">
-        <v>158558602</v>
+        <v>15853902</v>
       </c>
       <c r="AK3" t="n">
-        <v>162092809</v>
+        <v>16208926</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575237631797791</v>
+        <v>0.957314133644104</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098227620124817</v>
+        <v>0.9094545841217041</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8571126461029053</v>
+        <v>0.8562752604484558</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6610390543937683</v>
+        <v>0.6597946286201477</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013901948928833</v>
+        <v>0.900970458984375</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03212849016620213</v>
       </c>
       <c r="C4" t="n">
-        <v>637</v>
+        <v>93</v>
       </c>
       <c r="D4" t="n">
-        <v>7648355</v>
+        <v>1269717</v>
       </c>
       <c r="E4" t="n">
-        <v>23336422</v>
+        <v>1743863</v>
       </c>
       <c r="F4" t="n">
-        <v>1665954</v>
+        <v>249004</v>
       </c>
       <c r="G4" t="n">
-        <v>100587</v>
+        <v>22564</v>
       </c>
       <c r="H4" t="n">
-        <v>181589</v>
+        <v>38397</v>
       </c>
       <c r="I4" t="n">
-        <v>19776</v>
+        <v>4747</v>
       </c>
       <c r="J4" t="n">
-        <v>9264</v>
+        <v>909</v>
       </c>
       <c r="K4" t="n">
-        <v>8239829</v>
+        <v>1401780</v>
       </c>
       <c r="L4" t="n">
-        <v>9306506</v>
+        <v>1405771</v>
       </c>
       <c r="M4" t="n">
-        <v>3077252</v>
+        <v>481319</v>
       </c>
       <c r="N4" t="n">
-        <v>876221</v>
+        <v>120882</v>
       </c>
       <c r="O4" t="n">
-        <v>1459593</v>
+        <v>218746</v>
       </c>
       <c r="P4" t="n">
-        <v>330603</v>
+        <v>48514</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999269843101501</v>
+        <v>0.9999284148216248</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8581758141517639</v>
+        <v>0.7679348587989807</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7115169763565063</v>
+        <v>0.5383939146995544</v>
       </c>
       <c r="T4" t="n">
-        <v>0.600645899772644</v>
+        <v>0.4067472517490387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1909594535827637</v>
+        <v>0.07710370421409607</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6532679796218872</v>
+        <v>0.4397028982639313</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7085688710212708</v>
+        <v>0.4867168664932251</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2072431</v>
+        <v>211003</v>
       </c>
       <c r="Z4" t="n">
-        <v>29981680</v>
+        <v>3027015</v>
       </c>
       <c r="AA4" t="n">
-        <v>831668</v>
+        <v>83549</v>
       </c>
       <c r="AB4" t="n">
-        <v>55444</v>
+        <v>5619</v>
       </c>
       <c r="AC4" t="n">
-        <v>11417</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2219228</v>
+        <v>225793</v>
       </c>
       <c r="AG4" t="n">
-        <v>2909869</v>
+        <v>291779</v>
       </c>
       <c r="AH4" t="n">
-        <v>1328156</v>
+        <v>133576</v>
       </c>
       <c r="AI4" t="n">
-        <v>302625</v>
+        <v>30510</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499817</v>
+        <v>50160</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567984938621521</v>
+        <v>0.9561448693275452</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106762409210205</v>
+        <v>0.9107667803764343</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575728535652161</v>
+        <v>0.8571337461471558</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613578200340271</v>
+        <v>0.6601651310920715</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016773700714111</v>
+        <v>0.9014432430267334</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>418637</v>
+        <v>98416</v>
       </c>
       <c r="E5" t="n">
-        <v>2650215</v>
+        <v>346042</v>
       </c>
       <c r="F5" t="n">
-        <v>5340802</v>
+        <v>363498</v>
       </c>
       <c r="G5" t="n">
-        <v>285294</v>
+        <v>35016</v>
       </c>
       <c r="H5" t="n">
-        <v>601212</v>
+        <v>86386</v>
       </c>
       <c r="I5" t="n">
-        <v>69153</v>
+        <v>13147</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6338685</v>
+        <v>1010956</v>
       </c>
       <c r="L5" t="n">
-        <v>9616898</v>
+        <v>1584522</v>
       </c>
       <c r="M5" t="n">
-        <v>4024673</v>
+        <v>579026</v>
       </c>
       <c r="N5" t="n">
-        <v>708344</v>
+        <v>81523</v>
       </c>
       <c r="O5" t="n">
-        <v>1918910</v>
+        <v>306026</v>
       </c>
       <c r="P5" t="n">
-        <v>691758</v>
+        <v>115868</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999435544013977</v>
+        <v>0.9999446272850037</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9111932516098022</v>
+        <v>0.8530253171920776</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8847258687019348</v>
+        <v>0.8178427815437317</v>
       </c>
       <c r="T5" t="n">
-        <v>0.956737756729126</v>
+        <v>0.935407817363739</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9903474450111389</v>
+        <v>0.9876702427864075</v>
       </c>
       <c r="V5" t="n">
-        <v>0.979419469833374</v>
+        <v>0.9680328965187073</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9937721490859985</v>
+        <v>0.9899864792823792</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80954</v>
+        <v>8141</v>
       </c>
       <c r="Z5" t="n">
-        <v>859027</v>
+        <v>87332</v>
       </c>
       <c r="AA5" t="n">
-        <v>8027267</v>
+        <v>807060</v>
       </c>
       <c r="AB5" t="n">
-        <v>99883</v>
+        <v>10049</v>
       </c>
       <c r="AC5" t="n">
-        <v>292014</v>
+        <v>29309</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2142751</v>
+        <v>213557</v>
       </c>
       <c r="AG5" t="n">
-        <v>2971640</v>
+        <v>301370</v>
       </c>
       <c r="AH5" t="n">
-        <v>1338208</v>
+        <v>135464</v>
       </c>
       <c r="AI5" t="n">
-        <v>303488</v>
+        <v>30611</v>
       </c>
       <c r="AJ5" t="n">
-        <v>503066</v>
+        <v>50697</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.97342848777771</v>
+        <v>0.9732365012168884</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641720652580261</v>
+        <v>0.9638676047325134</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837575554847717</v>
+        <v>0.9836111068725586</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963077902793884</v>
+        <v>0.9962767362594604</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938908219337463</v>
+        <v>0.9938561916351318</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998381495475769</v>
+        <v>0.9983761310577393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>431</v>
+        <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>140252</v>
+        <v>20195</v>
       </c>
       <c r="E6" t="n">
-        <v>207467</v>
+        <v>24396</v>
       </c>
       <c r="F6" t="n">
-        <v>249259</v>
+        <v>25936</v>
       </c>
       <c r="G6" t="n">
-        <v>187004</v>
+        <v>8455</v>
       </c>
       <c r="H6" t="n">
-        <v>101152</v>
+        <v>9498</v>
       </c>
       <c r="I6" t="n">
-        <v>9783</v>
+        <v>1457</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65324</v>
+        <v>6613</v>
       </c>
       <c r="Z6" t="n">
-        <v>53793</v>
+        <v>5390</v>
       </c>
       <c r="AA6" t="n">
-        <v>109579</v>
+        <v>11097</v>
       </c>
       <c r="AB6" t="n">
-        <v>591860</v>
+        <v>59367</v>
       </c>
       <c r="AC6" t="n">
-        <v>69982</v>
+        <v>7030</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>169</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>31230</v>
+        <v>12691</v>
       </c>
       <c r="E7" t="n">
-        <v>318079</v>
+        <v>75891</v>
       </c>
       <c r="F7" t="n">
-        <v>897746</v>
+        <v>137552</v>
       </c>
       <c r="G7" t="n">
-        <v>440755</v>
+        <v>51047</v>
       </c>
       <c r="H7" t="n">
-        <v>3182671</v>
+        <v>205912</v>
       </c>
       <c r="I7" t="n">
-        <v>230931</v>
+        <v>28839</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>239</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8106</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>298070</v>
+        <v>30121</v>
       </c>
       <c r="AB7" t="n">
-        <v>76193</v>
+        <v>7701</v>
       </c>
       <c r="AC7" t="n">
-        <v>4598515</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>886</v>
+        <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>1355</v>
+        <v>761</v>
       </c>
       <c r="E8" t="n">
-        <v>29090</v>
+        <v>8848</v>
       </c>
       <c r="F8" t="n">
-        <v>66840</v>
+        <v>17784</v>
       </c>
       <c r="G8" t="n">
-        <v>31977</v>
+        <v>7930</v>
       </c>
       <c r="H8" t="n">
-        <v>561610</v>
+        <v>80502</v>
       </c>
       <c r="I8" t="n">
-        <v>1242855</v>
+        <v>77937</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
